--- a/output/stock_quant_scores/META_balance_df.xlsx
+++ b/output/stock_quant_scores/META_balance_df.xlsx
@@ -1625,30 +1625,42 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>13873000000</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>45531000000</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>124879000000</v>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>69761000000</v>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>41108000000</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>21135000000</v>
+      </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
         <v>382000000</v>
@@ -1670,7 +1682,9 @@
       </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>165987000000</v>
+      </c>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
@@ -1694,7 +1708,9 @@
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
+      <c r="BJ6" t="n">
+        <v>66666000000</v>
+      </c>
       <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="n">
         <v>2381000000</v>
@@ -1709,7 +1725,9 @@
       </c>
       <c r="BQ6" t="inlineStr"/>
       <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
+      <c r="BS6" t="n">
+        <v>16601000000</v>
+      </c>
       <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
     </row>
